--- a/VerveStacks_BIH_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BIH_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BIH_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14BCC7B6-E1C2-4C33-A9C0-EBDDC2B2ADF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4C83F42-60C4-49BC-8F7C-E38013F20E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{C89AC922-C6C1-473F-90AD-354DAA07953D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{C78E0D99-6D91-4169-81BD-0C5CCEBE6E44}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="130">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -87,34 +87,46 @@
     <t>e_Doboj_BIH</t>
   </si>
   <si>
-    <t>g_Doboj_BIH-Bijeljina_BIH</t>
+    <t>e_Tuzla_BIH</t>
+  </si>
+  <si>
+    <t>g_Doboj_BIH-Tuzla_BIH</t>
   </si>
   <si>
     <t>e_Mostar_BIH</t>
   </si>
   <si>
+    <t>e_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>g_Mostar_BIH-Sarajevo_BIH</t>
+  </si>
+  <si>
     <t>e_Trebinje_BIH</t>
   </si>
   <si>
     <t>g_Mostar_BIH-Trebinje_BIH</t>
   </si>
   <si>
-    <t>e_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>g_Mostar_BIH-Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>e_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>g_Mostar_BIH-Zenica_BIH</t>
+    <t>e_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>g_Orasje_BIH-Bijeljina_BIH</t>
+  </si>
+  <si>
+    <t>g_Orasje_BIH-Doboj_BIH</t>
   </si>
   <si>
     <t>e_Prijedor_BIH</t>
   </si>
   <si>
-    <t>g_Prijedor_BIH-Zenica_BIH</t>
+    <t>g_Prijedor_BIH-Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>g_Sarajevo_BIH-Bratunac_BIH</t>
+  </si>
+  <si>
+    <t>g_Sarajevo_BIH-Tuzla_BIH</t>
   </si>
   <si>
     <t>e_SirokiBrijeg_BIH</t>
@@ -123,7 +135,19 @@
     <t>g_SirokiBrijeg_BIH-Mostar_BIH</t>
   </si>
   <si>
-    <t>g_SirokiBrijeg_BIH-Zenica_BIH</t>
+    <t>g_SirokiBrijeg_BIH-Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>e_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>g_SirokiBrijeg_BIH-Travnik_BIH</t>
+  </si>
+  <si>
+    <t>g_Travnik_BIH-Mostar_BIH</t>
+  </si>
+  <si>
+    <t>g_Travnik_BIH-Prijedor_BIH</t>
   </si>
   <si>
     <t>g_Trebinje_BIH-Bratunac_BIH</t>
@@ -132,28 +156,16 @@
     <t>g_Trebinje_BIH-Mostar_BIH</t>
   </si>
   <si>
-    <t>e_Tuzla_BIH</t>
-  </si>
-  <si>
     <t>g_Tuzla_BIH-Bijeljina_BIH</t>
   </si>
   <si>
-    <t>g_Tuzla_BIH-Doboj_BIH</t>
+    <t>g_Tuzla_BIH-Orasje_BIH</t>
   </si>
   <si>
     <t>g_Tuzla_BIH-Prijedor_BIH</t>
   </si>
   <si>
-    <t>g_Tuzla_BIH-Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>g_Vogosca_BIH-Bratunac_BIH</t>
-  </si>
-  <si>
-    <t>g_Zenica_BIH-Prijedor_BIH</t>
-  </si>
-  <si>
-    <t>g_Zenica_BIH-Tuzla_BIH</t>
+    <t>g_Tuzla_BIH-Sarajevo_BIH</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -168,25 +180,43 @@
     <t>grid link -93.0 km- BA19-220;way/222962996-400</t>
   </si>
   <si>
-    <t>grid link -98.0 km- way/222962996-400;way/692824732-220</t>
+    <t>grid link -48.0 km- BA9-220;way/692824732-220</t>
+  </si>
+  <si>
+    <t>grid link -95.0 km- BA17-220;way/89827347-400</t>
   </si>
   <si>
     <t>grid link -69.0 km- way/245190169-400;way/89827347-400</t>
   </si>
   <si>
-    <t>grid link -97.0 km- way/175002028-400;way/89827347-400</t>
-  </si>
-  <si>
-    <t>grid link -89.0 km- BA11-220;way/89827347-400</t>
-  </si>
-  <si>
-    <t>grid link -174.0 km- BA11-220;way/79818891-220</t>
-  </si>
-  <si>
-    <t>grid link -113.0 km- BA26-220;way/89827347-400</t>
-  </si>
-  <si>
-    <t>grid link -92.0 km- BA11-220;BA26-220</t>
+    <t>grid link -98.0 km- BA4-220;way/222962996-400</t>
+  </si>
+  <si>
+    <t>grid link -46.0 km- BA4-220;way/692824732-220</t>
+  </si>
+  <si>
+    <t>grid link -174.0 km- BA17-220;way/79818891-220</t>
+  </si>
+  <si>
+    <t>grid link -130.0 km- BA17-220;BA19-220</t>
+  </si>
+  <si>
+    <t>grid link -67.0 km- BA17-220;BA9-220</t>
+  </si>
+  <si>
+    <t>grid link -46.0 km- BA26-220;way/89827347-400</t>
+  </si>
+  <si>
+    <t>grid link -61.0 km- BA17-220;BA26-220</t>
+  </si>
+  <si>
+    <t>grid link -92.0 km- BA26-220;way/251735977-220</t>
+  </si>
+  <si>
+    <t>grid link -113.0 km- way/251735977-220;way/89827347-400</t>
+  </si>
+  <si>
+    <t>grid link -96.0 km- way/251735977-220;way/79818891-220</t>
   </si>
   <si>
     <t>grid link -49.0 km- BA19-220;way/245190169-400</t>
@@ -195,25 +225,16 @@
     <t>grid link -84.0 km- way/245190169-400;way/89827347-400</t>
   </si>
   <si>
-    <t>grid link -42.0 km- way/222962996-400;way/841600752-220</t>
-  </si>
-  <si>
-    <t>grid link -70.0 km- way/692824732-220;way/841600752-220</t>
-  </si>
-  <si>
-    <t>grid link -136.0 km- way/79818891-220;way/841600752-220</t>
-  </si>
-  <si>
-    <t>grid link -87.0 km- way/175002028-400;way/841600752-220</t>
-  </si>
-  <si>
-    <t>grid link -130.0 km- BA19-220;way/175002028-400</t>
-  </si>
-  <si>
-    <t>grid link -96.0 km- BA11-220;way/79818891-220</t>
-  </si>
-  <si>
-    <t>grid link -71.0 km- BA11-220;way/841600752-220</t>
+    <t>grid link -42.0 km- BA9-220;way/222962996-400</t>
+  </si>
+  <si>
+    <t>grid link -92.0 km- BA4-220;BA9-220</t>
+  </si>
+  <si>
+    <t>grid link -136.0 km- BA9-220;way/79818891-220</t>
+  </si>
+  <si>
+    <t>grid link -84.0 km- BA17-220;BA9-220</t>
   </si>
   <si>
     <t>~commodity_geo</t>
@@ -324,12 +345,6 @@
     <t>p_co2_Mostar_BIH-ogci11364</t>
   </si>
   <si>
-    <t>co2_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>p_co2_Vogosca_BIH-ogci11364</t>
-  </si>
-  <si>
     <t>co2_Bijeljina_BIH</t>
   </si>
   <si>
@@ -342,6 +357,12 @@
     <t>p_co2_Trebinje_BIH-ogci11364</t>
   </si>
   <si>
+    <t>co2_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>p_co2_Travnik_BIH-ogci11364</t>
+  </si>
+  <si>
     <t>co2_Doboj_BIH</t>
   </si>
   <si>
@@ -360,46 +381,55 @@
     <t>p_co2_Bratunac_BIH-ogci11364</t>
   </si>
   <si>
-    <t>co2_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>p_co2_Zenica_BIH-ogci11364</t>
-  </si>
-  <si>
     <t>co2_SirokiBrijeg_BIH</t>
   </si>
   <si>
     <t>p_co2_SirokiBrijeg_BIH-ogci11364</t>
   </si>
   <si>
+    <t>co2_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>p_co2_Orasje_BIH-ogci11364</t>
+  </si>
+  <si>
+    <t>co2_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>p_co2_Sarajevo_BIH-ogci11364</t>
+  </si>
+  <si>
     <t>co2 pipeline -177 km- way/79818891-220 to ogci_11364.0</t>
   </si>
   <si>
     <t>co2 pipeline -105 km- way/89827347-400 to ogci_11364.0</t>
   </si>
   <si>
-    <t>co2 pipeline -30 km- way/175002028-400 to ogci_11364.0</t>
-  </si>
-  <si>
     <t>co2 pipeline -118 km- way/222962996-400 to ogci_11364.0</t>
   </si>
   <si>
     <t>co2 pipeline -185 km- way/245190169-400 to ogci_11364.0</t>
   </si>
   <si>
+    <t>co2 pipeline -88 km- way/251735977-220 to ogci_11364.0</t>
+  </si>
+  <si>
     <t>co2 pipeline -118 km- way/692824732-220 to ogci_11364.0</t>
   </si>
   <si>
-    <t>co2 pipeline -79 km- way/841600752-220 to ogci_11364.0</t>
+    <t>co2 pipeline -75 km- BA9-220 to ogci_11364.0</t>
   </si>
   <si>
     <t>co2 pipeline -135 km- BA19-220 to ogci_11364.0</t>
   </si>
   <si>
-    <t>co2 pipeline -22 km- BA11-220 to ogci_11364.0</t>
-  </si>
-  <si>
     <t>co2 pipeline -62 km- BA26-220 to ogci_11364.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -168 km- BA4-220 to ogci_11364.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -3 km- BA17-220 to ogci_11364.0</t>
   </si>
 </sst>
 </file>
@@ -770,8 +800,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE0D10FC-CE80-4CE9-A9A0-345573E1682E}">
-  <dimension ref="B3:R38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4813A4A7-1448-47D5-878C-3B813BC88564}">
+  <dimension ref="B3:R39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.45">
@@ -779,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.45">
@@ -808,22 +838,22 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="P4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="R4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.45">
@@ -852,7 +882,7 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O5" t="s">
         <v>10</v>
@@ -881,19 +911,19 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O6" t="s">
         <v>11</v>
@@ -919,22 +949,22 @@
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H7" t="s">
         <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="O7" t="s">
         <v>14</v>
@@ -960,25 +990,25 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="O8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P8" t="s">
         <v>8</v>
@@ -1001,34 +1031,34 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
         <v>13</v>
       </c>
       <c r="K9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" t="s">
+        <v>49</v>
+      </c>
+      <c r="O9" t="s">
         <v>22</v>
       </c>
-      <c r="L9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O9" t="s">
-        <v>23</v>
-      </c>
       <c r="P9" t="s">
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>16.71876991179986</v>
+        <v>18.42110605005314</v>
       </c>
       <c r="R9">
-        <v>44.940994050093479</v>
+        <v>45.287890541117157</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.45">
@@ -1042,10 +1072,10 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
         <v>24</v>
@@ -1057,7 +1087,7 @@
         <v>24</v>
       </c>
       <c r="L10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O10" t="s">
         <v>25</v>
@@ -1066,10 +1096,10 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>17.754869598202237</v>
+        <v>16.71876991179986</v>
       </c>
       <c r="R10">
-        <v>43.66018690912891</v>
+        <v>44.940994050093479</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.45">
@@ -1086,7 +1116,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
         <v>26</v>
@@ -1098,19 +1128,19 @@
         <v>26</v>
       </c>
       <c r="L11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P11" t="s">
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>18.333420931217962</v>
+        <v>18.123210349406762</v>
       </c>
       <c r="R11">
-        <v>42.677365387414312</v>
+        <v>44.036557460947769</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.45">
@@ -1124,10 +1154,10 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G12" t="s">
         <v>27</v>
@@ -1139,19 +1169,19 @@
         <v>27</v>
       </c>
       <c r="L12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P12" t="s">
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>18.604885316340617</v>
+        <v>17.754869598202237</v>
       </c>
       <c r="R12">
-        <v>44.52231833808716</v>
+        <v>43.66018690912891</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.45">
@@ -1165,10 +1195,10 @@
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -1180,19 +1210,19 @@
         <v>28</v>
       </c>
       <c r="L13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O13" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="P13" t="s">
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>18.315516969695064</v>
+        <v>17.264451011210998</v>
       </c>
       <c r="R13">
-        <v>43.882748242161547</v>
+        <v>44.328637955431432</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.45">
@@ -1206,34 +1236,34 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" t="s">
         <v>17</v>
       </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="O14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P14" t="s">
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>17.971015340419711</v>
+        <v>18.333420931217962</v>
       </c>
       <c r="R14">
-        <v>44.185989089314205</v>
+        <v>42.677365387414312</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.45">
@@ -1247,10 +1277,10 @@
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G15" t="s">
         <v>31</v>
@@ -1262,19 +1292,19 @@
         <v>31</v>
       </c>
       <c r="L15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O15" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="P15" t="s">
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>16.848113788793327</v>
+        <v>18.605783043969407</v>
       </c>
       <c r="R15">
-        <v>44.057613976118681</v>
+        <v>44.480477614181083</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.45">
@@ -1288,34 +1318,34 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
       </c>
       <c r="K16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="O16" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="P16" t="s">
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>17.378143623572235</v>
+        <v>16.848113788793327</v>
       </c>
       <c r="R16">
-        <v>43.465260169133238</v>
+        <v>44.057613976118681</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.45">
@@ -1329,34 +1359,34 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L17" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O17" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="P17" t="s">
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>18.311731015800159</v>
+        <v>17.378143623572235</v>
       </c>
       <c r="R17">
-        <v>42.956173893431625</v>
+        <v>43.465260169133238</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.45">
@@ -1370,34 +1400,34 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L18" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O18" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P18" t="s">
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>17.444108263455796</v>
+        <v>18.311731015800159</v>
       </c>
       <c r="R18">
-        <v>43.87828927556837</v>
+        <v>42.956173893431625</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.45">
@@ -1411,34 +1441,34 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" t="s">
         <v>13</v>
       </c>
       <c r="K19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="O19" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="P19" t="s">
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>18.276658083463406</v>
+        <v>17.444108263455796</v>
       </c>
       <c r="R19">
-        <v>43.428769171441658</v>
+        <v>43.87828927556837</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.45">
@@ -1452,34 +1482,34 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
       </c>
       <c r="K20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L20" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O20" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="P20" t="s">
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>15.978434643716612</v>
+        <v>18.276658083463406</v>
       </c>
       <c r="R20">
-        <v>45.002744611515183</v>
+        <v>43.428769171441658</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.45">
@@ -1493,235 +1523,316 @@
         <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
       </c>
       <c r="K21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L21" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="O21" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="P21" t="s">
         <v>8</v>
       </c>
       <c r="Q21">
+        <v>15.978434643716612</v>
+      </c>
+      <c r="R21">
+        <v>45.002744611515183</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K22" t="s">
+        <v>39</v>
+      </c>
+      <c r="L22" t="s">
+        <v>62</v>
+      </c>
+      <c r="O22" t="s">
+        <v>76</v>
+      </c>
+      <c r="P22" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22">
         <v>16.29623575978405</v>
       </c>
-      <c r="R21">
+      <c r="R22">
         <v>44.606501079376017</v>
       </c>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O22" t="s">
-        <v>70</v>
-      </c>
-      <c r="P22" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" t="s">
+        <v>40</v>
+      </c>
+      <c r="L23" t="s">
+        <v>63</v>
+      </c>
+      <c r="O23" t="s">
+        <v>77</v>
+      </c>
+      <c r="P23" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23">
         <v>16.942960342572068</v>
       </c>
-      <c r="R22">
+      <c r="R23">
         <v>44.609096263080872</v>
       </c>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O23" t="s">
-        <v>71</v>
-      </c>
-      <c r="P23" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q23">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" t="s">
+        <v>41</v>
+      </c>
+      <c r="L24" t="s">
+        <v>64</v>
+      </c>
+      <c r="O24" t="s">
+        <v>78</v>
+      </c>
+      <c r="P24" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24">
         <v>16.748007185771105</v>
       </c>
-      <c r="R23">
+      <c r="R24">
         <v>45.047603057243791</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O24" t="s">
-        <v>72</v>
-      </c>
-      <c r="P24" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q24">
-        <v>18.295289706978242</v>
-      </c>
-      <c r="R24">
-        <v>43.893677292673466</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O25" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="P25" t="s">
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>19.110860975704451</v>
+        <v>18.295289706978242</v>
       </c>
       <c r="R25">
-        <v>43.887694891985447</v>
+        <v>43.893677292673466</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O26" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P26" t="s">
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>18.816376843269349</v>
+        <v>19.110860975704451</v>
       </c>
       <c r="R26">
-        <v>44.55016652983371</v>
+        <v>43.887694891985447</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O27" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="P27" t="s">
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>17.765851307070299</v>
+        <v>18.816376843269349</v>
       </c>
       <c r="R27">
-        <v>44.618887511604576</v>
+        <v>44.55016652983371</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O28" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="P28" t="s">
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>18.005228691426183</v>
+        <v>17.765851307070299</v>
       </c>
       <c r="R28">
-        <v>44.925715954776898</v>
+        <v>44.618887511604576</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O29" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="P29" t="s">
         <v>8</v>
       </c>
       <c r="Q29">
-        <v>18.32197152564548</v>
+        <v>18.005228691426183</v>
       </c>
       <c r="R29">
-        <v>42.953405544278802</v>
+        <v>44.925715954776898</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O30" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="P30" t="s">
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>18.627262293368485</v>
+        <v>18.32197152564548</v>
       </c>
       <c r="R30">
-        <v>43.127075227327843</v>
+        <v>42.953405544278802</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O31" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="P31" t="s">
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>18.016680757922487</v>
+        <v>18.627262293368485</v>
       </c>
       <c r="R31">
-        <v>42.948063383468678</v>
+        <v>43.127075227327843</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O32" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="P32" t="s">
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>17.711389990199486</v>
+        <v>18.016680757922487</v>
       </c>
       <c r="R32">
-        <v>43.127075227327843</v>
+        <v>42.948063383468678</v>
       </c>
     </row>
     <row r="33" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O33" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P33" t="s">
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>18.627262293368485</v>
+        <v>17.711389990199486</v>
       </c>
       <c r="R33">
-        <v>44.925715954776905</v>
+        <v>43.127075227327843</v>
       </c>
     </row>
     <row r="34" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O34" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="P34" t="s">
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>19.23784382881448</v>
+        <v>18.627262293368485</v>
       </c>
       <c r="R34">
-        <v>44.700885863845777</v>
+        <v>44.925715954776905</v>
       </c>
     </row>
     <row r="35" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O35" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P35" t="s">
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>16.184936151584491</v>
+        <v>19.23784382881448</v>
       </c>
       <c r="R35">
-        <v>44.476055772914641</v>
+        <v>44.700885863845777</v>
       </c>
     </row>
     <row r="36" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O36" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P36" t="s">
         <v>8</v>
@@ -1730,34 +1841,48 @@
         <v>16.184936151584491</v>
       </c>
       <c r="R36">
-        <v>44.700885863845777</v>
+        <v>44.476055772914641</v>
       </c>
     </row>
     <row r="37" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O37" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="P37" t="s">
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>17.054788284677237</v>
+        <v>16.184936151584491</v>
       </c>
       <c r="R37">
-        <v>43.851912946765857</v>
+        <v>44.700885863845777</v>
       </c>
     </row>
     <row r="38" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O38" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="P38" t="s">
         <v>8</v>
       </c>
       <c r="Q38">
+        <v>17.054788284677237</v>
+      </c>
+      <c r="R38">
+        <v>43.851912946765857</v>
+      </c>
+    </row>
+    <row r="39" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O39" t="s">
+        <v>93</v>
+      </c>
+      <c r="P39" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q39">
         <v>16.795517687030493</v>
       </c>
-      <c r="R38">
+      <c r="R39">
         <v>43.801565500121242</v>
       </c>
     </row>
@@ -1767,8 +1892,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4F5A1C1-8BFC-45CB-AA30-579EFE01925D}">
-  <dimension ref="B3:L14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9D31E1-657C-49E9-9BBD-56153D3E2949}">
+  <dimension ref="B3:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
@@ -1776,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
@@ -1802,10 +1927,10 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
@@ -1816,25 +1941,25 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G5" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K5" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L5" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -1845,25 +1970,25 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="L6" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -1874,25 +1999,25 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G7" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K7" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L7" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
@@ -1903,25 +2028,25 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" t="s">
         <v>96</v>
       </c>
-      <c r="F8" t="s">
-        <v>89</v>
-      </c>
       <c r="G8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L8" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
@@ -1932,25 +2057,25 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" t="s">
         <v>98</v>
       </c>
-      <c r="F9" t="s">
-        <v>89</v>
-      </c>
-      <c r="G9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H9" t="s">
-        <v>91</v>
-      </c>
       <c r="K9" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L9" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -1961,25 +2086,25 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G10" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K10" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L10" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
@@ -1990,25 +2115,25 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G11" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H11" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K11" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
@@ -2019,25 +2144,25 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F12" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G12" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H12" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K12" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L12" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -2048,25 +2173,25 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F13" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G13" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="H13" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K13" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L13" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
@@ -2077,25 +2202,54 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F14" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H14" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L14" t="s">
-        <v>119</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" t="s">
+        <v>98</v>
+      </c>
+      <c r="K15" t="s">
+        <v>118</v>
+      </c>
+      <c r="L15" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
